--- a/dataset_t6_grouped/results2/G5/G5_T6588_W0053F0003T0006Z000C1N46_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T6588_W0053F0003T0006Z000C1N46_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>4.968703555135707</v>
+        <v>0.8074143277095523</v>
       </c>
       <c r="D2" t="n">
-        <v>4.607966932056789</v>
+        <v>0.7487946264592283</v>
       </c>
       <c r="E2" t="n">
-        <v>13.32621982832537</v>
+        <v>2.165510722102872</v>
       </c>
       <c r="F2" t="n">
-        <v>11.47801730418166</v>
+        <v>1.865177811929519</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>31.62114321178644</v>
+        <v>5.138435771915296</v>
       </c>
       <c r="D3" t="n">
-        <v>27.5640015404201</v>
+        <v>4.479150250318266</v>
       </c>
       <c r="E3" t="n">
-        <v>13.32621982832537</v>
+        <v>2.165510722102872</v>
       </c>
       <c r="F3" t="n">
-        <v>11.47801730418166</v>
+        <v>1.865177811929519</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
